--- a/EDA/exposure/exposure_tables.xlsx
+++ b/EDA/exposure/exposure_tables.xlsx
@@ -591,7 +591,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-10T13:23:01</t>
+          <t>2026-09-13T19:48:30</t>
         </is>
       </c>
     </row>
